--- a/Configs/形象role.xlsx
+++ b/Configs/形象role.xlsx
@@ -1,40 +1,489 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="role_config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="role_config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>animator</t>
+  </si>
+  <si>
+    <t>prefabPath</t>
+  </si>
+  <si>
+    <t>portraitPath</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>星际守卫</t>
+  </si>
+  <si>
+    <t>Characters/Hero/skull_man</t>
+  </si>
+  <si>
+    <t>Prefabs/actors/Hero</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>小型异形</t>
+  </si>
+  <si>
+    <t>Characters/Monster/skull_goblin</t>
+  </si>
+  <si>
+    <t>Prefabs/actors/Monster</t>
+  </si>
+  <si>
+    <t>中型异形</t>
+  </si>
+  <si>
+    <t>大型异形</t>
+  </si>
+  <si>
+    <t>异形精锐</t>
+  </si>
+  <si>
+    <t>虚空侍卫</t>
+  </si>
+  <si>
+    <t>虚空领主</t>
+  </si>
+  <si>
+    <t>Characters/Boss/skull_warrior</t>
+  </si>
+  <si>
+    <t>Prefabs/actors/Boss</t>
+  </si>
+  <si>
+    <t>Portrait/void_lord</t>
+  </si>
+  <si>
+    <t>深渊守卫</t>
+  </si>
+  <si>
+    <t>Portrait/abyss_guard</t>
+  </si>
+  <si>
+    <t>虚空暴君</t>
+  </si>
+  <si>
+    <t>Portrait/void_tyrant</t>
+  </si>
+  <si>
+    <t>风影守卫</t>
+  </si>
+  <si>
+    <t>Characters/Summon/skull_slime</t>
+  </si>
+  <si>
+    <t>Prefabs/actors/Summon</t>
+  </si>
+  <si>
+    <t>熔岩守卫</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,17 +491,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -335,252 +1080,243 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="32.625" customWidth="1"/>
+    <col min="4" max="4" width="24.875" customWidth="1"/>
+    <col min="5" max="5" width="22.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>prefabPath</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>portraitPath</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>星际守卫</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Hero</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>101</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>小型异形</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Monster</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>102</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>中型异形</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Monster</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>103</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>大型异形</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Monster</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>110</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>异形精锐</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Monster</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>111</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>虚空侍卫</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Monster</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>200</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>虚空领主</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Boss</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Portrait/void_lord</t>
-        </is>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>201</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>深渊守卫</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Boss</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Portrait/abyss_guard</t>
-        </is>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11">
         <v>202</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>虚空暴君</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Boss</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Portrait/void_tyrant</t>
-        </is>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12">
         <v>1001</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>风影守卫</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Summon</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13">
         <v>1002</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>熔岩守卫</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Prefabs/actors/Summon</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Configs/形象role.xlsx
+++ b/Configs/形象role.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -35,13 +35,10 @@
     <t>name</t>
   </si>
   <si>
-    <t>animator</t>
-  </si>
-  <si>
     <t>prefabPath</t>
   </si>
   <si>
-    <t>portraitPath</t>
+    <t>head</t>
   </si>
   <si>
     <t>int</t>
@@ -129,14 +126,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,148 +582,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1101,31 +1091,27 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1"/>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
+      <c r="C2"/>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1133,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1150,16 +1136,16 @@
         <v>101</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1167,16 +1153,16 @@
         <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1184,16 +1170,16 @@
         <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1201,16 +1187,16 @@
         <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1218,16 +1204,16 @@
         <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1235,16 +1221,16 @@
         <v>200</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1252,16 +1238,16 @@
         <v>201</v>
       </c>
       <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1269,16 +1255,16 @@
         <v>202</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1286,16 +1272,16 @@
         <v>1001</v>
       </c>
       <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1303,16 +1289,16 @@
         <v>1002</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/形象role.xlsx
+++ b/Configs/形象role.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -38,6 +38,12 @@
     <t>prefabPath</t>
   </si>
   <si>
+    <t>animatorPath</t>
+  </si>
+  <si>
+    <t>sprite_set</t>
+  </si>
+  <si>
     <t>head</t>
   </si>
   <si>
@@ -47,27 +53,36 @@
     <t>string</t>
   </si>
   <si>
+    <t>{int slotType;string spritePath}[]</t>
+  </si>
+  <si>
     <t>星际守卫</t>
   </si>
   <si>
-    <t>Characters/Hero/skull_man</t>
-  </si>
-  <si>
     <t>Prefabs/actors/Hero</t>
   </si>
   <si>
+    <t>Hero/Animations/skull_hero</t>
+  </si>
+  <si>
+    <t>0~Hero/Sprites/Weapon-Sword|1~Hero/Sprites/Hat-Helmet|2~Hero/Sprites/Head|3~Hero/Sprites/body|4~Hero/Sprites/Leg</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
     <t>小型异形</t>
   </si>
   <si>
-    <t>Characters/Monster/skull_goblin</t>
-  </si>
-  <si>
     <t>Prefabs/actors/Monster</t>
   </si>
   <si>
+    <t>Monster/Animations/skull_monster</t>
+  </si>
+  <si>
+    <t>0~Monster/Sprites/Weapon-Sword|1~Monster/Sprites/Hat-Helmet|2~Monster/Sprites/Head|3~Monster/Sprites/body|4~Monster/Sprites/Leg</t>
+  </si>
+  <si>
     <t>中型异形</t>
   </si>
   <si>
@@ -83,12 +98,15 @@
     <t>虚空领主</t>
   </si>
   <si>
-    <t>Characters/Boss/skull_warrior</t>
-  </si>
-  <si>
     <t>Prefabs/actors/Boss</t>
   </si>
   <si>
+    <t>Boss/Animations/skull_boss</t>
+  </si>
+  <si>
+    <t>0~Boss/Sprites/Weapon-Sword|1~Boss/Sprites/Hat-Helmet|2~Boss/Sprites/Head|3~Boss/Sprites/body|4~Boss/Sprites/Leg</t>
+  </si>
+  <si>
     <t>Portrait/void_lord</t>
   </si>
   <si>
@@ -107,10 +125,13 @@
     <t>风影守卫</t>
   </si>
   <si>
-    <t>Characters/Summon/skull_slime</t>
-  </si>
-  <si>
     <t>Prefabs/actors/Summon</t>
+  </si>
+  <si>
+    <t>Summon/Animations/skull_summon</t>
+  </si>
+  <si>
+    <t>0~Summon/Sprites/Weapon-Sword|1~Summon/Sprites/Hat-Helmet|2~Summon/Sprites/Head|3~Summon/Sprites/body|4~Summon/Sprites/Leg</t>
   </si>
   <si>
     <t>熔岩守卫</t>
@@ -729,7 +750,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1076,229 +1099,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
-    <col min="4" max="4" width="24.875" customWidth="1"/>
-    <col min="5" max="5" width="22.625" customWidth="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="24.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="56" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1"/>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2"/>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
+    <row r="3" ht="40.5" spans="1:6">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
+    <row r="4" ht="40.5" spans="1:6">
+      <c r="A4" s="1">
         <v>101</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
+    <row r="5" ht="40.5" spans="1:6">
+      <c r="A5" s="1">
         <v>102</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
+    <row r="6" ht="40.5" spans="1:6">
+      <c r="A6" s="1">
         <v>103</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
+    <row r="7" ht="40.5" spans="1:6">
+      <c r="A7" s="1">
         <v>110</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
+    <row r="8" ht="40.5" spans="1:6">
+      <c r="A8" s="1">
         <v>111</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
+    <row r="9" ht="40.5" spans="1:6">
+      <c r="A9" s="1">
         <v>200</v>
       </c>
-      <c r="B9" t="s">
-        <v>17</v>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
+    <row r="10" ht="40.5" spans="1:6">
+      <c r="A10" s="1">
         <v>201</v>
       </c>
-      <c r="B10" t="s">
-        <v>21</v>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
+    <row r="11" ht="40.5" spans="1:6">
+      <c r="A11" s="1">
         <v>202</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
+    <row r="12" ht="40.5" spans="1:6">
+      <c r="A12" s="1">
         <v>1001</v>
       </c>
-      <c r="B12" t="s">
-        <v>25</v>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
+        <v>32</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
+    <row r="13" ht="40.5" spans="1:6">
+      <c r="A13" s="1">
         <v>1002</v>
       </c>
-      <c r="B13" t="s">
-        <v>28</v>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
+        <v>32</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
